--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00888-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00888-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C50F859-ACB6-40D3-8A4B-E62AA5B96EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{39A6F162-3B25-4887-B116-0EEE5268FD4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{38146F62-A56B-49DF-867E-5EDBC3E7A3E8}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{45E5B7C2-D372-4ABD-86A9-BBD55270CF3F}"/>
   </bookViews>
   <sheets>
     <sheet name="00888-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1570,25 +1570,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025FE0CD-C928-469F-95E5-009BC330338F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED078624-0992-4D24-8F9E-710C6BA48FB5}">
   <dimension ref="A1:R30"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1616,7 +1616,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1646,7 +1646,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1742,7 +1742,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>8.99</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1822,7 +1822,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1878,7 +1878,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>6.71</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>2.4700000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2100,7 +2100,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
         <v>2024</v>
       </c>
@@ -2210,7 +2210,7 @@
         <v>4.5999999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -2322,7 +2322,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>27</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>27</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="49">
         <v>2023</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>6.08</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>27</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2656,7 +2656,7 @@
         <v>1.53</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2022</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
@@ -2822,7 +2822,7 @@
         <v>1.79</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
@@ -2878,7 +2878,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>27</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>27</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="49">
         <v>2021</v>
       </c>
@@ -3044,7 +3044,7 @@
         <v>2.72</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>27</v>
       </c>
@@ -3100,7 +3100,7 @@
         <v>2.72</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="51" t="s">
         <v>61</v>
       </c>
